--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ADC BOADILLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ADC BOADILLA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8456</v>
+        <v>29.078</v>
       </c>
       <c r="E2" t="n">
-        <v>20.872</v>
+        <v>33.8345</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.0262</v>
+        <v>-4.7562</v>
       </c>
       <c r="G2" t="n">
         <v>-22.2617</v>
@@ -610,13 +610,13 @@
         <v>73.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-36.2057</v>
+        <v>-17.9732</v>
       </c>
       <c r="T2" t="n">
-        <v>-25.6045</v>
+        <v>-12.6418</v>
       </c>
       <c r="U2" t="n">
-        <v>-10.601</v>
+        <v>-5.3317</v>
       </c>
       <c r="V2" t="n">
         <v>56.3127</v>
@@ -649,7 +649,7 @@
         <v>1.9237</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02060000000000001</v>
+        <v>-0.0206</v>
       </c>
       <c r="G3" t="n">
         <v>2.0035</v>
@@ -688,13 +688,13 @@
         <v>0.388</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2064</v>
+        <v>-0.2063</v>
       </c>
       <c r="T3" t="n">
         <v>-0.3029</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0965</v>
+        <v>0.0964</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7696</v>
+        <v>0.5148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3367</v>
+        <v>0.1365</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4329</v>
+        <v>0.3783</v>
       </c>
       <c r="G4" t="n">
         <v>3.7164</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3517</v>
+        <v>0.097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3286</v>
+        <v>0.1284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0231</v>
+        <v>-0.0314</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MINGO CERVERA</t>
+          <t>I. SOTO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,61 +874,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.406</v>
+        <v>-0.3489</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.4171</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.406</v>
+        <v>1.0682</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.406</v>
+        <v>-0.4063</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.4523</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.406</v>
+        <v>-0.8586</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.2442</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.0092</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.2534</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.406</v>
+        <v>-0.1621</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.5569</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.406</v>
+        <v>0.3948</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.0575</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2028</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2602</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>P. MINGO CERVERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4314</v>
+        <v>-0.406</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0192</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.4506</v>
+        <v>-0.406</v>
       </c>
       <c r="G7" t="n">
-        <v>8.326699999999999</v>
+        <v>-0.406</v>
       </c>
       <c r="H7" t="n">
-        <v>2.316799999999999</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6.009900000000001</v>
+        <v>-0.406</v>
       </c>
       <c r="J7" t="n">
-        <v>16.3706</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>11.8062</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.5644</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.043900000000001</v>
+        <v>-0.406</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.489699999999999</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4458</v>
+        <v>-0.406</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.388</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.1048</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>15.7166</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.213200000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8952</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.1086</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.1568</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8581</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. SOTO RODRIGUEZ</t>
+          <t>S. HERRERO GALVEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5640999999999999</v>
+        <v>-1.0295</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5778</v>
+        <v>2.8297</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0137</v>
+        <v>-3.8593</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4063</v>
+        <v>0.4138999999999998</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4523</v>
+        <v>0.1425000000000002</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8586</v>
+        <v>0.2712999999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2442</v>
+        <v>4.4991</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0092</v>
+        <v>4.4612</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2534</v>
+        <v>0.03789999999999982</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1621</v>
+        <v>-4.0852</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5569</v>
+        <v>-4.3188</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3948</v>
+        <v>0.2335000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5821000000000003</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-3.8807</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>4.4627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1577</v>
+        <v>-1.6001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3634</v>
+        <v>-0.4231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2057</v>
+        <v>-1.177</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.4253</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.6344</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2909</v>
+        <v>-1.2181</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3773</v>
+        <v>-0.2772</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9137</v>
+        <v>-0.9409</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4214</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5397</v>
+        <v>-0.4669</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V9" t="n">
         <v>0.2821</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HERRERO GALVEZ</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7994</v>
+        <v>-2.514899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4688</v>
+        <v>3.5983</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2681</v>
+        <v>-6.1133</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4138999999999998</v>
+        <v>8.326699999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1425000000000002</v>
+        <v>2.316799999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2712999999999998</v>
+        <v>6.009900000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4991</v>
+        <v>16.3706</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4612</v>
+        <v>11.8062</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03789999999999982</v>
+        <v>4.5644</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0852</v>
+        <v>-8.043900000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.3188</v>
+        <v>-9.489699999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2335000000000001</v>
+        <v>1.4458</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5821000000000003</v>
+        <v>-0.388</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8807</v>
+        <v>-16.1048</v>
       </c>
       <c r="R10" t="n">
-        <v>4.4627</v>
+        <v>15.7166</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.37</v>
+        <v>-4.2968</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.784</v>
+        <v>-0.5257000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.586</v>
+        <v>-3.771</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4253</v>
+        <v>-6.1568</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6344</v>
+        <v>3.8581</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0597</v>
+        <v>-10.015</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.072900000000001</v>
+        <v>-5.9484</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8854</v>
+        <v>-2.7853</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1874</v>
+        <v>-3.1629</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5652</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8375</v>
+        <v>-0.7131</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.969</v>
+        <v>-0.8689</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1314</v>
+        <v>0.1559</v>
       </c>
       <c r="V11" t="n">
         <v>-1.506</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.7354</v>
+        <v>-6.176600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4527</v>
+        <v>-3.1909</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2828</v>
+        <v>-2.9858</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8123</v>
@@ -1390,13 +1390,13 @@
         <v>3.6866</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.5709</v>
+        <v>-2.0121</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2039</v>
+        <v>-0.9422</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3669</v>
+        <v>-1.0699</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1284</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GIRALDO SISTIAGA</t>
+          <t>I. FINI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.4497</v>
+        <v>-9.189300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.5693</v>
+        <v>-5.2467</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8806</v>
+        <v>-3.9425</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.143599999999999</v>
+        <v>-2.4339</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.1439</v>
+        <v>-4.5509</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9998</v>
+        <v>2.1172</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4132</v>
+        <v>-0.01639999999999993</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1194999999999999</v>
+        <v>-0.1482</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5326</v>
+        <v>0.1317999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.7305</v>
+        <v>-2.4177</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.2634</v>
+        <v>-4.4028</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4671</v>
+        <v>1.9853</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1941</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.821</v>
+        <v>-5.238799999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>6.015</v>
+        <v>3.6867</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8196</v>
+        <v>-3.7449</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2993</v>
+        <v>-1.2153</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4797</v>
+        <v>-2.5296</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3194</v>
+        <v>-1.4582</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9641</v>
+        <v>1.2239</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6448</v>
+        <v>-2.6821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. FINI</t>
+          <t>J. GIRALDO SISTIAGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.6348</v>
+        <v>-9.767799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.446800000000001</v>
+        <v>-6.2875</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.188</v>
+        <v>-3.4801</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.4339</v>
+        <v>-9.143599999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.5509</v>
+        <v>-7.1439</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1172</v>
+        <v>-1.9998</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.01639999999999993</v>
+        <v>-1.4132</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1482</v>
+        <v>0.1194999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1317999999999999</v>
+        <v>-1.5326</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4177</v>
+        <v>-7.7305</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.4028</v>
+        <v>-7.2634</v>
       </c>
       <c r="O14" t="n">
-        <v>1.9853</v>
+        <v>-0.4671</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5523</v>
+        <v>0.1941</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.238799999999999</v>
+        <v>-5.821</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6867</v>
+        <v>6.015</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.1904</v>
+        <v>-2.1374</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4155</v>
+        <v>-2.0175</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7749</v>
+        <v>-0.12</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4582</v>
+        <v>1.3194</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2239</v>
+        <v>2.9641</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6821</v>
+        <v>-1.6448</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.3737</v>
+        <v>-21.9875</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.123999999999999</v>
+        <v>-8.6167</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.2503</v>
+        <v>-13.3708</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8498</v>
+        <v>-0.5154000000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9894000000000006</v>
+        <v>-0.5485999999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8600000000000003</v>
+        <v>0.03339999999999987</v>
       </c>
       <c r="J15" t="n">
-        <v>34.5749</v>
+        <v>13.9285</v>
       </c>
       <c r="K15" t="n">
-        <v>27.6207</v>
+        <v>8.189299999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>6.9542</v>
+        <v>5.739199999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-36.4248</v>
+        <v>-14.4443</v>
       </c>
       <c r="N15" t="n">
-        <v>-28.6105</v>
+        <v>-8.738099999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.814</v>
+        <v>-5.7059</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5820000000000007</v>
+        <v>-8.5375</v>
       </c>
       <c r="Q15" t="n">
-        <v>-53.7471</v>
+        <v>-24.4483</v>
       </c>
       <c r="R15" t="n">
-        <v>53.165</v>
+        <v>15.9106</v>
       </c>
       <c r="S15" t="n">
-        <v>13.6803</v>
+        <v>-0.6869</v>
       </c>
       <c r="T15" t="n">
-        <v>7.390099999999999</v>
+        <v>-1.2957</v>
       </c>
       <c r="U15" t="n">
-        <v>6.2901</v>
+        <v>0.6087</v>
       </c>
       <c r="V15" t="n">
-        <v>-23.6226</v>
+        <v>-12.2473</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6582</v>
+        <v>3.1985</v>
       </c>
       <c r="X15" t="n">
-        <v>-27.2805</v>
+        <v>-15.446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-19.2404</v>
+        <v>-26.4587</v>
       </c>
       <c r="E16" t="n">
-        <v>-11.4042</v>
+        <v>-12.7934</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.8363</v>
+        <v>-13.6656</v>
       </c>
       <c r="G16" t="n">
-        <v>-32.7462</v>
+        <v>-10.5504</v>
       </c>
       <c r="H16" t="n">
-        <v>-18.2487</v>
+        <v>-4.1595</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.4973</v>
+        <v>-6.390699999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2247</v>
+        <v>21.9048</v>
       </c>
       <c r="K16" t="n">
-        <v>8.8079</v>
+        <v>19.9753</v>
       </c>
       <c r="L16" t="n">
-        <v>-6.583100000000001</v>
+        <v>1.929599999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-34.9706</v>
+        <v>-32.4553</v>
       </c>
       <c r="N16" t="n">
-        <v>-27.0566</v>
+        <v>-24.1352</v>
       </c>
       <c r="O16" t="n">
-        <v>-7.914300000000001</v>
+        <v>-8.3202</v>
       </c>
       <c r="P16" t="n">
-        <v>7.7612</v>
+        <v>-0.7761000000000007</v>
       </c>
       <c r="Q16" t="n">
-        <v>-39.5826</v>
+        <v>-45.9858</v>
       </c>
       <c r="R16" t="n">
-        <v>47.3438</v>
+        <v>45.2095</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5303</v>
+        <v>-6.4532</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6242</v>
+        <v>-4.188400000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9057000000000001</v>
+        <v>-2.2649</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2142</v>
+        <v>-8.678999999999998</v>
       </c>
       <c r="W16" t="n">
-        <v>24.3297</v>
+        <v>15.476</v>
       </c>
       <c r="X16" t="n">
-        <v>-21.1152</v>
+        <v>-24.1547</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.1698</v>
+        <v>-27.2347</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.019299999999999</v>
+        <v>-17.0065</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.1508</v>
+        <v>-10.2281</v>
       </c>
       <c r="G17" t="n">
-        <v>-16.1094</v>
+        <v>-1.8498</v>
       </c>
       <c r="H17" t="n">
-        <v>-9.071</v>
+        <v>-0.9894000000000006</v>
       </c>
       <c r="I17" t="n">
-        <v>-7.0383</v>
+        <v>-0.8600000000000003</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9081999999999999</v>
+        <v>34.5749</v>
       </c>
       <c r="K17" t="n">
-        <v>5.24</v>
+        <v>27.6207</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.148</v>
+        <v>6.9542</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.2008</v>
+        <v>-36.4248</v>
       </c>
       <c r="N17" t="n">
-        <v>-14.3109</v>
+        <v>-28.6105</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8899999999999999</v>
+        <v>-7.814</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7164</v>
+        <v>-0.5820000000000007</v>
       </c>
       <c r="Q17" t="n">
-        <v>-13.5824</v>
+        <v>-53.7471</v>
       </c>
       <c r="R17" t="n">
-        <v>16.2988</v>
+        <v>53.165</v>
       </c>
       <c r="S17" t="n">
-        <v>6.8512</v>
+        <v>-1.1805</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5924</v>
+        <v>-1.4926</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2589</v>
+        <v>0.3119000000000003</v>
       </c>
       <c r="V17" t="n">
-        <v>-14.6283</v>
+        <v>-23.6226</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8791</v>
+        <v>3.6582</v>
       </c>
       <c r="X17" t="n">
-        <v>-16.5073</v>
+        <v>-27.2805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VILASANCHEZ FREIJOMIL</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-24.4576</v>
+        <v>-27.4201</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.599</v>
+        <v>-17.0809</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.8585</v>
+        <v>-10.3391</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5154000000000002</v>
+        <v>-32.7462</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5485999999999998</v>
+        <v>-18.2487</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03339999999999987</v>
+        <v>-14.4973</v>
       </c>
       <c r="J18" t="n">
-        <v>13.9285</v>
+        <v>2.2247</v>
       </c>
       <c r="K18" t="n">
-        <v>8.189299999999999</v>
+        <v>8.8079</v>
       </c>
       <c r="L18" t="n">
-        <v>5.739199999999999</v>
+        <v>-6.583100000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-14.4443</v>
+        <v>-34.9706</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.738099999999999</v>
+        <v>-27.0566</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.7059</v>
+        <v>-7.914300000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-8.5375</v>
+        <v>7.7612</v>
       </c>
       <c r="Q18" t="n">
-        <v>-24.4483</v>
+        <v>-39.5826</v>
       </c>
       <c r="R18" t="n">
-        <v>15.9106</v>
+        <v>47.3438</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.1573</v>
+        <v>-5.6493</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.2781</v>
+        <v>-4.0529</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.879</v>
+        <v>-1.5971</v>
       </c>
       <c r="V18" t="n">
-        <v>-12.2473</v>
+        <v>3.2142</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1985</v>
+        <v>24.3297</v>
       </c>
       <c r="X18" t="n">
-        <v>-15.446</v>
+        <v>-21.1152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-24.8905</v>
+        <v>-27.9876</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.7569</v>
+        <v>-12.8637</v>
       </c>
       <c r="F19" t="n">
-        <v>-14.1338</v>
+        <v>-15.1244</v>
       </c>
       <c r="G19" t="n">
-        <v>-10.5504</v>
+        <v>-16.1094</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.1595</v>
+        <v>-9.071</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.390699999999999</v>
+        <v>-7.0383</v>
       </c>
       <c r="J19" t="n">
-        <v>21.9048</v>
+        <v>-0.9081999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>19.9753</v>
+        <v>5.24</v>
       </c>
       <c r="L19" t="n">
-        <v>1.929599999999999</v>
+        <v>-6.148</v>
       </c>
       <c r="M19" t="n">
-        <v>-32.4553</v>
+        <v>-15.2008</v>
       </c>
       <c r="N19" t="n">
-        <v>-24.1352</v>
+        <v>-14.3109</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.3202</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761000000000007</v>
+        <v>2.7164</v>
       </c>
       <c r="Q19" t="n">
-        <v>-45.9858</v>
+        <v>-13.5824</v>
       </c>
       <c r="R19" t="n">
-        <v>45.2095</v>
+        <v>16.2988</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.885</v>
+        <v>0.03329999999999997</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.1518</v>
+        <v>-0.2520000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.7331</v>
+        <v>0.2854000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-8.678999999999998</v>
+        <v>-14.6283</v>
       </c>
       <c r="W19" t="n">
-        <v>15.476</v>
+        <v>1.8791</v>
       </c>
       <c r="X19" t="n">
-        <v>-24.1547</v>
+        <v>-16.5073</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>-37.4467</v>
+        <v>-33.8584</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.6853</v>
+        <v>-17.9389</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.7615</v>
+        <v>-15.9193</v>
       </c>
       <c r="G20" t="n">
         <v>-16.5564</v>
@@ -2014,13 +2014,13 @@
         <v>12.806</v>
       </c>
       <c r="S20" t="n">
-        <v>-8.5829</v>
+        <v>-4.9942</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.8933</v>
+        <v>-2.1471</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.6894</v>
+        <v>-2.8475</v>
       </c>
       <c r="V20" t="n">
         <v>-6.8745</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-45.46</v>
+        <v>-34.7824</v>
       </c>
       <c r="E21" t="n">
-        <v>-27.1555</v>
+        <v>-22.2849</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.3046</v>
+        <v>-12.497</v>
       </c>
       <c r="G21" t="n">
         <v>-24.2861</v>
@@ -2092,13 +2092,13 @@
         <v>38.0302</v>
       </c>
       <c r="S21" t="n">
-        <v>-21.8532</v>
+        <v>-11.1754</v>
       </c>
       <c r="T21" t="n">
-        <v>-12.4111</v>
+        <v>-7.5406</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.4422</v>
+        <v>-3.6349</v>
       </c>
       <c r="V21" t="n">
         <v>-4.754200000000001</v>
@@ -2125,13 +2125,13 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>-47.0597</v>
+        <v>-40.4326</v>
       </c>
       <c r="E22" t="n">
-        <v>-15.9814</v>
+        <v>-13.8532</v>
       </c>
       <c r="F22" t="n">
-        <v>-31.0784</v>
+        <v>-26.5792</v>
       </c>
       <c r="G22" t="n">
         <v>-13.0571</v>
@@ -2170,13 +2170,13 @@
         <v>39.7769</v>
       </c>
       <c r="S22" t="n">
-        <v>-14.5521</v>
+        <v>-7.925</v>
       </c>
       <c r="T22" t="n">
-        <v>-8.068099999999999</v>
+        <v>-5.9401</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.484</v>
+        <v>-1.9852</v>
       </c>
       <c r="V22" t="n">
         <v>-3.5396</v>
@@ -2203,13 +2203,13 @@
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>-61.2176</v>
+        <v>-53.5756</v>
       </c>
       <c r="E23" t="n">
-        <v>-40.822</v>
+        <v>-35.2534</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.3956</v>
+        <v>-18.3222</v>
       </c>
       <c r="G23" t="n">
         <v>-12.5241</v>
@@ -2248,13 +2248,13 @@
         <v>34.7321</v>
       </c>
       <c r="S23" t="n">
-        <v>-17.3659</v>
+        <v>-9.724</v>
       </c>
       <c r="T23" t="n">
-        <v>-13.0434</v>
+        <v>-7.4748</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.3226</v>
+        <v>-2.2494</v>
       </c>
       <c r="V23" t="n">
         <v>-18.3278</v>
@@ -2281,13 +2281,13 @@
         <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>-317.9883</v>
+        <v>-298.6472</v>
       </c>
       <c r="E24" t="n">
-        <v>-141.2365</v>
+        <v>-134.5736</v>
       </c>
       <c r="F24" t="n">
-        <v>-176.7532</v>
+        <v>-164.0728</v>
       </c>
       <c r="G24" t="n">
         <v>-156.0513</v>
@@ -2299,13 +2299,13 @@
         <v>-27.6663</v>
       </c>
       <c r="J24" t="n">
-        <v>177.2109</v>
+        <v>177.2109000000001</v>
       </c>
       <c r="K24" t="n">
         <v>138.4147</v>
       </c>
       <c r="L24" t="n">
-        <v>38.79639999999999</v>
+        <v>38.7964</v>
       </c>
       <c r="M24" t="n">
         <v>-333.2617</v>
@@ -2314,7 +2314,7 @@
         <v>-266.7991</v>
       </c>
       <c r="O24" t="n">
-        <v>-66.46180000000001</v>
+        <v>-66.4618</v>
       </c>
       <c r="P24" t="n">
         <v>-19.4032</v>
@@ -2326,13 +2326,13 @@
         <v>414.2592999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-100.0334</v>
+        <v>-80.69090000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-60.38180000000001</v>
+        <v>-53.7199</v>
       </c>
       <c r="U24" t="n">
-        <v>-39.6517</v>
+        <v>-26.9735</v>
       </c>
       <c r="V24" t="n">
         <v>-42.5017</v>
